--- a/test_data/WTA/WTA Calculator - CIT Calculator/WTA Calculator - CIT Calculator_Test_Cases.xlsx
+++ b/test_data/WTA/WTA Calculator - CIT Calculator/WTA Calculator - CIT Calculator_Test_Cases.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +47,11 @@
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -60,7 +65,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -69,6 +74,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -436,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -628,7 +636,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>CIT_03</t>
+          <t>CIT_06</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -638,12 +646,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>'Domestic Jurisdiction' lists real countries</t>
+          <t>Entering Taxable Income for BD/2024 computes the correct Total CIT</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Opening 'Domestic Jurisdiction' must list real country names including Bangladesh.</t>
+          <t>With Bangladesh / 01 July 2024-30 June 2025 selected and Taxable Income=100,000 entered (then blurred), Total CIT must compute to 55,000 = 100,000 x 55% (the known, live-confirmed Bangladesh/2024 HeadlineRate).</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -653,41 +661,41 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Domestic Jurisdiction: Bangladesh, Tax Year: 2024-2025, Taxable Income: 100000</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1. Log in, open CIT Calculator
-2. Open 'Domestic Jurisdiction'
-3. Verify real countries are listed</t>
+          <t>1. Log in, open CIT Calculator, select Bangladesh/2024-2025
+2. Enter Taxable Income=100000 and blur the field
+3. Verify Total CIT computes to 55,000</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Opening 'Domestic Jurisdiction' must list real country names including Bangladesh.</t>
+          <t>With Bangladesh / 01 July 2024-30 June 2025 selected and Taxable Income=100,000 entered (then blurred), Total CIT must compute to 55,000 = 100,000 x 55% (the known, live-confirmed Bangladesh/2024 HeadlineRate).</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>'Domestic Jurisdiction' correctly lists 120 real countries.</t>
+          <t>Total CIT did not compute as expected (got '27500').</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>[PASS] 'Domestic Jurisdiction' lists real countries including Bangladesh</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>[FAIL] Total CIT computes to the expected value</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>CIT_04</t>
+          <t>CIT_07</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -697,56 +705,56 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>'Tax Year' lists real date-range options</t>
+          <t>Total tax due and Nominal ETR match an independent API-sourced calculation</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>After selecting a Domestic Jurisdiction, 'Tax Year' must list real date-range options (e.g. '01 July 2024 - 30 June 2025'), not plain year numbers.</t>
+          <t>With Bangladesh/2024-2025/Taxable Income=100,000, Total tax due and Nominal ETR must match an independent calculation using the live CorporateRate API's own HeadlineRate for BD/2024 - not compared against the UI itself.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, Bangladesh selected as Domestic Jurisdiction.</t>
+          <t>User is logged in.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Domestic Jurisdiction: Bangladesh</t>
+          <t>Domestic Jurisdiction: Bangladesh, Tax Year: 2024-2025, Taxable Income: 100000</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1. Log in, open CIT Calculator, select Bangladesh
-2. Open 'Tax Year'
-3. Verify real date-range options are listed</t>
+          <t>1. Log in, open CIT Calculator, select Bangladesh/2024-2025, enter Taxable Income=100000
+2. Independently fetch the live CorporateRate API for BD/2024
+3. Verify Total tax due and Nominal ETR match the independently-fetched rate</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>After selecting a Domestic Jurisdiction, 'Tax Year' must list real date-range options (e.g. '01 July 2024 - 30 June 2025'), not plain year numbers.</t>
+          <t>With Bangladesh/2024-2025/Taxable Income=100,000, Total tax due and Nominal ETR must match an independent calculation using the live CorporateRate API's own HeadlineRate for BD/2024 - not compared against the UI itself.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>'Tax Year' correctly lists 16 real date-range options (e.g. '01 July 2026 - 30 June 2027').</t>
+          <t>Results did not match the independent API calculation (ui total_due=27500.00/etr=27.5, expected total_due=55000.0/etr=55.0).</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>[PASS] 'Tax Year' lists real date-range options</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>[FAIL] Total tax due and Nominal ETR match the independently-fetched API rate</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>CIT_05</t>
+          <t>CIT_10</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -756,12 +764,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>A jurisdiction/year with no rate data shows a blocking message</t>
+          <t>Switching to 'By Entity' swaps in Corporate Group/Entity fields</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Selecting Australia / 01 July 2023-30 June 2024 (a confirmed live null-HeadlineRate combination, same documented data gap as Corporate Rate Finder's CRF_09) must show a modal reading 'No data found for this jurisdiction. You may try for another jurisdiction.' (Cancel-only) - this is real, documented application behavior, not an automation bug.</t>
+          <t>Clicking 'By Entity' must swap 'Domestic Jurisdiction' for 'Corporate Group' and 'Entity in Residence states' fields (confirmed live: this module's own naming, not 'Source Company' like other Calculator sub-pages).</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -771,28 +779,29 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Domestic Jurisdiction: Australia, Tax Year: 01 July 2023 - 30 June 2024</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1. Log in, open CIT Calculator, select Australia / 2023-2024
-2. Verify the 'No data found' blocking modal appears</t>
+          <t>1. Log in, open CIT Calculator
+2. Click 'By Entity'
+3. Verify 'Corporate Group' and 'Entity in Residence states' fields are visible</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Selecting Australia / 01 July 2023-30 June 2024 (a confirmed live null-HeadlineRate combination, same documented data gap as Corporate Rate Finder's CRF_09) must show a modal reading 'No data found for this jurisdiction. You may try for another jurisdiction.' (Cancel-only) - this is real, documented application behavior, not an automation bug.</t>
+          <t>Clicking 'By Entity' must swap 'Domestic Jurisdiction' for 'Corporate Group' and 'Entity in Residence states' fields (confirmed live: this module's own naming, not 'Source Company' like other Calculator sub-pages).</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Selecting a jurisdiction/year with no rate data correctly triggered the real blocking message.</t>
+          <t>Switching to 'By Entity' correctly swapped in the entity-based fields.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>[PASS] The no-rate-data modal shows the expected message with only Cancel</t>
+          <t>[PASS] 'By Entity' mode shows Corporate Group/Entity fields</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -804,7 +813,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>CIT_06</t>
+          <t>CIT_12</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -814,12 +823,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Entering Taxable Income for BD/2024 computes the correct Total CIT</t>
+          <t>'Start over' shows a confirmation dialog</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>With Bangladesh / 01 July 2024-30 June 2025 selected and Taxable Income=100,000 entered (then blurred), Total CIT must compute to 55,000 = 100,000 x 55% (the known, live-confirmed Bangladesh/2024 HeadlineRate).</t>
+          <t>Clicking 'Start over' must show a confirmation dialog reading 'Are you sure to reset all your selections?' with Cancel/Yes actions.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -829,443 +838,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Domestic Jurisdiction: Bangladesh, Tax Year: 2024-2025, Taxable Income: 100000</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open CIT Calculator, select Bangladesh/2024-2025
-2. Enter Taxable Income=100000 and blur the field
-3. Verify Total CIT computes to 55,000</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>With Bangladesh / 01 July 2024-30 June 2025 selected and Taxable Income=100,000 entered (then blurred), Total CIT must compute to 55,000 = 100,000 x 55% (the known, live-confirmed Bangladesh/2024 HeadlineRate).</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Total CIT correctly computed to 55000 (100,000 x 55%).</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Total CIT computes to the expected value</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CIT_07</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - CIT Calculator</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Total tax due and Nominal ETR match an independent API-sourced calculation</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>With Bangladesh/2024-2025/Taxable Income=100,000, Total tax due and Nominal ETR must match an independent calculation using the live CorporateRate API's own HeadlineRate for BD/2024 - not compared against the UI itself.</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Domestic Jurisdiction: Bangladesh, Tax Year: 2024-2025, Taxable Income: 100000</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open CIT Calculator, select Bangladesh/2024-2025, enter Taxable Income=100000
-2. Independently fetch the live CorporateRate API for BD/2024
-3. Verify Total tax due and Nominal ETR match the independently-fetched rate</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>With Bangladesh/2024-2025/Taxable Income=100,000, Total tax due and Nominal ETR must match an independent calculation using the live CorporateRate API's own HeadlineRate for BD/2024 - not compared against the UI itself.</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Total tax due (55000.00) and Nominal ETR (55) correctly matched the independently-fetched live API rate (55.0%).</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Total tax due and Nominal ETR match the independently-fetched API rate</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CIT_08</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - CIT Calculator</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Generate Memo/Get Forms/Add to Project become enabled once the calculation completes</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>After a successful BD/2024/100,000 calculation, the 3 action buttons must become enabled (they're present but disabled before the calculation completes).</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, BD/2024-2025/100,000 calculated.</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open CIT Calculator, complete BD/2024-2025/100,000
-2. Verify the 3 action buttons are enabled</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>After a successful BD/2024/100,000 calculation, the 3 action buttons must become enabled (they're present but disabled before the calculation completes).</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>All 3 action buttons correctly became enabled after calculation.</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] All 3 action buttons are enabled after calculation</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CIT_09</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - CIT Calculator</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>The Surtax/Surcharge section shows 'No surtax applicable' when none exists</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>For Bangladesh/2024-2025, the Surtax/Surcharge Rate section must show '* No surtax applicable' - a real, documented application behavior, not a missing feature.</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Bangladesh/2024-2025 selected.</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open CIT Calculator, select Bangladesh/2024-2025
-2. Verify the 'No surtax applicable' message is visible</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>For Bangladesh/2024-2025, the Surtax/Surcharge Rate section must show '* No surtax applicable' - a real, documented application behavior, not a missing feature.</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>The 'No surtax applicable' message is correctly shown for this jurisdiction/year.</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'No surtax applicable' is shown for Bangladesh/2024-2025</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CIT_10</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - CIT Calculator</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Switching to 'By Entity' swaps in Corporate Group/Entity fields</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'By Entity' must swap 'Domestic Jurisdiction' for 'Corporate Group' and 'Entity in Residence states' fields (confirmed live: this module's own naming, not 'Source Company' like other Calculator sub-pages).</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open CIT Calculator
-2. Click 'By Entity'
-3. Verify 'Corporate Group' and 'Entity in Residence states' fields are visible</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'By Entity' must swap 'Domestic Jurisdiction' for 'Corporate Group' and 'Entity in Residence states' fields (confirmed live: this module's own naming, not 'Source Company' like other Calculator sub-pages).</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Switching to 'By Entity' correctly swapped in the entity-based fields.</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'By Entity' mode shows Corporate Group/Entity fields</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CIT_11</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - CIT Calculator</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>'Corporate Group' lists this account's real entity charts</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>In 'By Entity' mode, opening 'Corporate Group' must list this account's real, previously-created entity charts.</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, 'By Entity' mode selected.</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open CIT Calculator, switch to 'By Entity'
-2. Open 'Corporate Group'
-3. Verify at least one real entity chart is listed</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>In 'By Entity' mode, opening 'Corporate Group' must list this account's real, previously-created entity charts.</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>'Corporate Group' correctly lists 20 real entity chart(s): ['Demo Entity Chart', 'Natmed', 'Empty', 'N', 'Empty Entity Chart', 'Copy of Demo Import Test', 'New Chart with 3rd Party', 'Testing Empty Chart', 'New AG', 'New 3423', 'new', 'testt', 'Royal Enfield Incorporation', 'Test MM', 'new v2', 'Blank', 'JHUMKAH', 'RETRS', 'chuppp', 'BEINTEHA'].</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'Corporate Group' lists at least one real entity chart</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CIT_12</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - CIT Calculator</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>'Start over' shows a confirmation dialog</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Start over' must show a confirmation dialog reading 'Are you sure to reset all your selections?' with Cancel/Yes actions.</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open CIT Calculator
 2. Click 'Start over'
 3. Verify the confirmation dialog</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Start over' must show a confirmation dialog reading 'Are you sure to reset all your selections?' with Cancel/Yes actions.</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>'Start over' correctly showed a confirmation dialog before resetting.</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Start over' shows the expected confirmation dialog</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CIT_13</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - CIT Calculator</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Confirming 'Start over' (Yes) resets the Domestic Jurisdiction selection</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Confirming 'Start over' with 'Yes' must reset the Domestic Jurisdiction select back to its 'Select' placeholder state.</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Bangladesh selected as Domestic Jurisdiction.</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Domestic Jurisdiction: Bangladesh</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open CIT Calculator, select Bangladesh
-2. Click 'Start over' then 'Yes'
-3. Verify Domestic Jurisdiction resets to 'Select'</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Confirming 'Start over' with 'Yes' must reset the Domestic Jurisdiction select back to its 'Select' placeholder state.</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Confirming 'Start over' correctly reset the selection to its placeholder state.</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Domestic Jurisdiction resets to the 'Select' placeholder</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
